--- a/doc/Tables.xlsx
+++ b/doc/Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wim/Desktop/projects/structuralism_simulation/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{550A2921-52B3-234B-9EEA-267106C4FDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF71EA2-8E11-2F43-89B1-7464B7C873E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2260" windowWidth="28040" windowHeight="17440" xr2:uid="{7281BCD8-63D2-1E4B-A6F9-F8D9D46CBE2B}"/>
   </bookViews>
@@ -72,16 +72,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -127,22 +125,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,90 +456,106 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF82C0A3-B4B9-6949-B692-D3C263CA7347}">
-  <dimension ref="B1:G6"/>
+  <dimension ref="B1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.33203125" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B1" s="3"/>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B1" s="1"/>
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B5" s="3"/>
-      <c r="C5" s="4" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="1"/>
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="2:7" ht="29" x14ac:dyDescent="0.2">
+      <c r="B6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
